--- a/inst/extdata/pe_2025.xlsx
+++ b/inst/extdata/pe_2025.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -52,10 +51,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -503,10 +503,10 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SPD003</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
+          <t>SPD0003</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
         <v>45698</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -514,17 +514,17 @@
           <t>Staphylococcus epidermidis</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="3" t="n">
         <v>45712</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SPD007</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
+          <t>SPD0007</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
         <v>45738</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -532,7 +532,7 @@
           <t>Culture negative</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="3" t="n">
         <v>45752</v>
       </c>
       <c r="E3" t="inlineStr">
@@ -547,10 +547,10 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SPD012</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
+          <t>SPD0012</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
         <v>45675</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -558,17 +558,17 @@
           <t>Escherichia coli</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="3" t="n">
         <v>45689</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SPD012</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
+          <t>SPD0012</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
         <v>45874</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -576,17 +576,17 @@
           <t>Staphylococcus aureus</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="3" t="n">
         <v>45888</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SPD018</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
+          <t>SPD0018</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
         <v>45791</v>
       </c>
       <c r="C6" t="inlineStr">
@@ -594,7 +594,7 @@
           <t>Klebsiella pneumoniae</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="3" t="n">
         <v>45805</v>
       </c>
       <c r="E6" t="inlineStr">
@@ -609,10 +609,10 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SPD023</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
+          <t>SPD0023</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
         <v>45749</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -620,17 +620,17 @@
           <t>Staphylococcus epidermidis</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="3" t="n">
         <v>45763</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SPD025</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
+          <t>SPD0025</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
         <v>45836</v>
       </c>
       <c r="C8" t="inlineStr">
@@ -638,17 +638,17 @@
           <t>Pseudomonas aeruginosa</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="3" t="n">
         <v>45850</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SPD030</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
+          <t>SPD0030</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
         <v>45915</v>
       </c>
       <c r="C9" t="inlineStr">
@@ -656,17 +656,17 @@
           <t>Enterococcus faecalis</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="3" t="n">
         <v>45929</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SPD033</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
+          <t>SPD0033</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
         <v>45849</v>
       </c>
       <c r="C10" t="inlineStr">
@@ -674,17 +674,17 @@
           <t>Culture negative</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" s="3" t="n">
         <v>45863</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SPD036</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
+          <t>SPD0036</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
         <v>45981</v>
       </c>
       <c r="C11" t="inlineStr">
@@ -692,17 +692,17 @@
           <t>Staphylococcus epidermidis</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" s="3" t="n">
         <v>45995</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SPD041</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
+          <t>SPD0041</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
         <v>45765</v>
       </c>
       <c r="C12" t="inlineStr">
@@ -710,17 +710,17 @@
           <t>Escherichia coli</t>
         </is>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="D12" s="3" t="n">
         <v>45779</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SPD044</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
+          <t>SPD0044</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
         <v>45868</v>
       </c>
       <c r="C13" t="inlineStr">
@@ -728,7 +728,7 @@
           <t>Staphylococcus aureus</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D13" s="3" t="n">
         <v>45882</v>
       </c>
       <c r="E13" t="inlineStr">
@@ -743,10 +743,10 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SPD047</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
+          <t>SPD0047</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
         <v>45935</v>
       </c>
       <c r="C14" t="inlineStr">
@@ -754,17 +754,17 @@
           <t>Staphylococcus epidermidis</t>
         </is>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D14" s="3" t="n">
         <v>45949</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SPD052</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
+          <t>SPD0052</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
         <v>45759</v>
       </c>
       <c r="C15" t="inlineStr">
@@ -772,7 +772,7 @@
           <t>Klebsiella pneumoniae</t>
         </is>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="D15" s="3" t="n">
         <v>45773</v>
       </c>
       <c r="E15" t="inlineStr">
@@ -787,10 +787,10 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SPD055</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
+          <t>SPD0055</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
         <v>45721</v>
       </c>
       <c r="C16" t="inlineStr">
@@ -798,17 +798,17 @@
           <t>Staphylococcus epidermidis</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="D16" s="3" t="n">
         <v>45735</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SPD056</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
+          <t>SPD0056</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
         <v>45823</v>
       </c>
       <c r="C17" t="inlineStr">
@@ -816,17 +816,17 @@
           <t>Enterococcus faecalis</t>
         </is>
       </c>
-      <c r="D17" s="2" t="n">
+      <c r="D17" s="3" t="n">
         <v>45837</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SPD058</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
+          <t>SPD0058</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
         <v>45797</v>
       </c>
       <c r="C18" t="inlineStr">
@@ -834,7 +834,7 @@
           <t>Culture negative</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n">
+      <c r="D18" s="3" t="n">
         <v>45811</v>
       </c>
       <c r="I18" t="inlineStr">
@@ -842,20 +842,20 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="K18" s="2" t="n">
+      <c r="K18" s="3" t="n">
         <v>45809</v>
       </c>
-      <c r="L18" s="2" t="n">
+      <c r="L18" s="3" t="n">
         <v>45823</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SPD025</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
+          <t>SPD0025</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
         <v>45976</v>
       </c>
       <c r="C19" t="inlineStr">
@@ -863,7 +863,7 @@
           <t>Staphylococcus epidermidis</t>
         </is>
       </c>
-      <c r="D19" s="2" t="n">
+      <c r="D19" s="3" t="n">
         <v>45990</v>
       </c>
     </row>

--- a/inst/extdata/pe_2025.xlsx
+++ b/inst/extdata/pe_2025.xlsx
@@ -16,8 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -421,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -867,6 +868,210 @@
         <v>45990</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SPD0003</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>45731</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Staphylococcus epidermidis</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>45745</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SPD0018</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>45826</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Klebsiella pneumoniae</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>45840</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SPD0033</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>45879</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Staphylococcus aureus</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>45893</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SPD0023</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>45783</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>45797</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SPD0030</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>45950</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Pseudomonas aeruginosa</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>45964</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SPD0046</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>45910</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Staphylococcus aureus</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SPD0046</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>45945</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Pseudomonas aeruginosa</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>45959</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SPD0047</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>45971</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>45985</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SPD0041</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>45848</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Escherichia coli</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>45862</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SPD0012</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>45920</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Staphylococcus aureus</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>45934</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
